--- a/jira_export_2026-10-06.xlsx
+++ b/jira_export_2026-10-06.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>1,243 €</t>
+          <t>1,519 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -767,7 +767,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>516 €</t>
+          <t>792 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>81 h</t>
+          <t>82 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>287</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -5980,8 +5980,8 @@
       <c r="N73" s="12" t="n">
         <v>276</v>
       </c>
-      <c r="O73" s="13" t="n">
-        <v>0</v>
+      <c r="O73" s="12" t="n">
+        <v>276</v>
       </c>
       <c r="P73" s="12" t="n">
         <v>0</v>
@@ -7549,7 +7549,7 @@
         <v>9</v>
       </c>
       <c r="K95" s="11" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="L95" s="11" t="inlineStr">
         <is>
@@ -9611,10 +9611,10 @@
         <v>123627.162</v>
       </c>
       <c r="O126" s="18" t="n">
-        <v>1242.9</v>
+        <v>1518.9</v>
       </c>
       <c r="P126" s="18" t="n">
-        <v>24.82</v>
+        <v>29.74</v>
       </c>
     </row>
   </sheetData>
@@ -10498,7 +10498,7 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>26.25</v>
+        <v>27.25</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>9.75</v>
@@ -10507,7 +10507,7 @@
         <v>1.08</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>37.08</v>
+        <v>38.08</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>5.5</v>
@@ -10517,7 +10517,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>7.5%</t>
         </is>
       </c>
     </row>
@@ -10644,19 +10644,19 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>497919</v>
+        <v>497643</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>203444</v>
+        <v>198140</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>294475</v>
+        <v>299503</v>
       </c>
       <c r="E5" s="24" t="n">
         <v>227001</v>
       </c>
       <c r="F5" s="24" t="n">
-        <v>22113</v>
+        <v>27141</v>
       </c>
       <c r="G5" s="24" t="n">
         <v>18055</v>
@@ -10694,19 +10694,19 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>241457</v>
+        <v>241181</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>143201</v>
+        <v>137897</v>
       </c>
       <c r="D7" s="26" t="n">
-        <v>98256</v>
+        <v>103284</v>
       </c>
       <c r="E7" s="26" t="n">
         <v>50106</v>
       </c>
       <c r="F7" s="26" t="n">
-        <v>12938</v>
+        <v>17966</v>
       </c>
       <c r="G7" s="26" t="n">
         <v>10431</v>
@@ -10723,7 +10723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -10747,7 +10747,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 3 commande(s)</t>
+          <t>Épics créées ce mois — 4 commande(s)</t>
         </is>
       </c>
     </row>
@@ -10802,22 +10802,22 @@
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-36181</t>
+          <t>PDMDEP-36214</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-36174</t>
+          <t>PDMDEP-36205</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE AURAY</t>
+          <t>COMME DE FECAMP</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -10837,7 +10837,7 @@
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>00183814</t>
+          <t>00176659</t>
         </is>
       </c>
       <c r="I5" s="25" t="n">
@@ -10847,12 +10847,12 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36197</t>
+          <t>PDMDEP-36181</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36190</t>
+          <t>PDMDEP-36174</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -10862,17 +10862,17 @@
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BAUGE-EN-ANJOU</t>
+          <t>COMMUNE DE AURAY</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
@@ -10882,7 +10882,7 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>00183894</t>
+          <t>00183814</t>
         </is>
       </c>
       <c r="I6" s="26" t="n">
@@ -10892,73 +10892,97 @@
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
+          <t>PDMDEP-36197</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-36190</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>COMMUNE DE BAUGE-EN-ANJOU</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H7" s="15" t="inlineStr">
+        <is>
+          <t>00183894</t>
+        </is>
+      </c>
+      <c r="I7" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
           <t>PDMDEP-36148</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>PDMDEP-36144</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>01/10/2026</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>VILLE DE VILLEFRANCHE SUR SAONE</t>
         </is>
       </c>
-      <c r="E7" s="15" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F7" s="15" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="G8" s="11" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H7" s="15" t="inlineStr">
+      <c r="H8" s="11" t="inlineStr">
         <is>
           <t>00183228</t>
         </is>
       </c>
-      <c r="I7" s="25" t="n">
-        <v>2310</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="n"/>
-      <c r="C8" s="17" t="n"/>
-      <c r="D8" s="17" t="n"/>
-      <c r="E8" s="17" t="n"/>
-      <c r="F8" s="17" t="n"/>
-      <c r="G8" s="17" t="n"/>
-      <c r="H8" s="17" t="inlineStr">
-        <is>
-          <t>3 commande(s)</t>
-        </is>
-      </c>
-      <c r="I8" s="24" t="n">
+      <c r="I8" s="26" t="n">
         <v>2310</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B9" s="17" t="n"/>
@@ -10969,7 +10993,7 @@
       <c r="G9" s="17" t="n"/>
       <c r="H9" s="17" t="inlineStr">
         <is>
-          <t>2 commande(s)</t>
+          <t>4 commande(s)</t>
         </is>
       </c>
       <c r="I9" s="24" t="n">
@@ -10979,7 +11003,7 @@
     <row r="10">
       <c r="A10" s="17" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B10" s="17" t="n"/>
@@ -10990,10 +11014,31 @@
       <c r="G10" s="17" t="n"/>
       <c r="H10" s="17" t="inlineStr">
         <is>
-          <t>1 commande(s)</t>
+          <t>2 commande(s)</t>
         </is>
       </c>
       <c r="I10" s="24" t="n">
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="17" t="n"/>
+      <c r="D11" s="17" t="n"/>
+      <c r="E11" s="17" t="n"/>
+      <c r="F11" s="17" t="n"/>
+      <c r="G11" s="17" t="n"/>
+      <c r="H11" s="17" t="inlineStr">
+        <is>
+          <t>2 commande(s)</t>
+        </is>
+      </c>
+      <c r="I11" s="24" t="n">
         <v>0</v>
       </c>
     </row>

--- a/jira_export_2026-10-06.xlsx
+++ b/jira_export_2026-10-06.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>82 h</t>
+          <t>86 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>288</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P126"/>
+  <dimension ref="A1:P130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -949,7 +949,7 @@
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
     <col width="26" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="N73" s="12" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="O73" s="12" t="n">
         <v>276</v>
@@ -8494,12 +8494,12 @@
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E109" s="11" t="n">
@@ -8527,34 +8527,34 @@
       </c>
       <c r="H109" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I109" s="11" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J109" s="11" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K109" s="11" t="n">
-        <v>0.5</v>
+        <v>0.19</v>
       </c>
       <c r="L109" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M109" s="11" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N109" s="12" t="n">
-        <v>250</v>
-      </c>
-      <c r="O109" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P109" s="12" t="n">
@@ -8564,22 +8564,22 @@
     <row r="110">
       <c r="A110" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B110" s="15" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C110" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D110" s="15" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E110" s="15" t="n">
@@ -8597,34 +8597,34 @@
       </c>
       <c r="H110" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I110" s="15" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J110" s="15" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K110" s="15" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="L110" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M110" s="15" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N110" s="16" t="n">
-        <v>230</v>
-      </c>
-      <c r="O110" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P110" s="16" t="n">
@@ -8634,22 +8634,22 @@
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E111" s="11" t="n">
@@ -8672,23 +8672,23 @@
       </c>
       <c r="I111" s="11" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J111" s="11" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K111" s="11" t="n">
-        <v>0.5</v>
+        <v>0.19</v>
       </c>
       <c r="L111" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28027</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M111" s="11" t="inlineStr">
         <is>
-          <t>470688</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N111" s="12" t="n">
@@ -8704,22 +8704,22 @@
     <row r="112">
       <c r="A112" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19792</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B112" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C112" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D112" s="15" t="inlineStr">
         <is>
-          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E112" s="15" t="n">
@@ -8742,23 +8742,23 @@
       </c>
       <c r="I112" s="15" t="inlineStr">
         <is>
-          <t>06/03/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J112" s="15" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K112" s="15" t="n">
-        <v>0.25</v>
+        <v>0.19</v>
       </c>
       <c r="L112" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27377</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M112" s="15" t="inlineStr">
         <is>
-          <t>478048</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N112" s="16" t="n">
@@ -8774,28 +8774,26 @@
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18954</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>Maisons-Alfort</t>
-        </is>
-      </c>
-      <c r="E113" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>MONTREUIL</t>
+        </is>
+      </c>
+      <c r="E113" s="11" t="n">
+        <v/>
       </c>
       <c r="F113" s="11" t="inlineStr">
         <is>
@@ -8804,7 +8802,7 @@
       </c>
       <c r="G113" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H113" s="11" t="inlineStr">
@@ -8814,21 +8812,29 @@
       </c>
       <c r="I113" s="11" t="inlineStr">
         <is>
-          <t>05/02/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J113" s="11" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K113" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L113" s="11" t="inlineStr"/>
-      <c r="M113" s="11" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L113" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28035</t>
+        </is>
+      </c>
+      <c r="M113" s="11" t="inlineStr">
+        <is>
+          <t>468660</t>
+        </is>
+      </c>
       <c r="N113" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O113" s="12" t="n">
+        <v>250</v>
+      </c>
+      <c r="O113" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P113" s="12" t="n">
@@ -8838,12 +8844,12 @@
     <row r="114">
       <c r="A114" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B114" s="15" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C114" s="15" t="inlineStr">
@@ -8853,7 +8859,7 @@
       </c>
       <c r="D114" s="15" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E114" s="15" t="n">
@@ -8866,31 +8872,39 @@
       </c>
       <c r="G114" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H114" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I114" s="15" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J114" s="15" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K114" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L114" s="15" t="inlineStr"/>
-      <c r="M114" s="15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L114" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28034</t>
+        </is>
+      </c>
+      <c r="M114" s="15" t="inlineStr">
+        <is>
+          <t>475575</t>
+        </is>
+      </c>
       <c r="N114" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O114" s="16" t="n">
+        <v>230</v>
+      </c>
+      <c r="O114" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P114" s="16" t="n">
@@ -8900,22 +8914,22 @@
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E115" s="11" t="n">
@@ -8923,7 +8937,7 @@
       </c>
       <c r="F115" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G115" s="11" t="inlineStr">
@@ -8933,34 +8947,34 @@
       </c>
       <c r="H115" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I115" s="11" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J115" s="11" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K115" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L115" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28019</t>
+          <t>PDMDEP-28027</t>
         </is>
       </c>
       <c r="M115" s="11" t="inlineStr">
         <is>
-          <t>455151</t>
+          <t>470688</t>
         </is>
       </c>
       <c r="N115" s="12" t="n">
-        <v>240</v>
-      </c>
-      <c r="O115" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O115" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P115" s="12" t="n">
@@ -8970,12 +8984,12 @@
     <row r="116">
       <c r="A116" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-19792</t>
         </is>
       </c>
       <c r="B116" s="15" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
         </is>
       </c>
       <c r="C116" s="15" t="inlineStr">
@@ -8985,7 +8999,7 @@
       </c>
       <c r="D116" s="15" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>VIENNE CONDRIEU AGGLOMERATION</t>
         </is>
       </c>
       <c r="E116" s="15" t="n">
@@ -9003,34 +9017,34 @@
       </c>
       <c r="H116" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I116" s="15" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>06/03/2025</t>
         </is>
       </c>
       <c r="J116" s="15" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K116" s="15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L116" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-27377</t>
         </is>
       </c>
       <c r="M116" s="15" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>478048</t>
         </is>
       </c>
       <c r="N116" s="16" t="n">
-        <v>557.145</v>
-      </c>
-      <c r="O116" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O116" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P116" s="16" t="n">
@@ -9040,26 +9054,28 @@
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-18954</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>CD Manche</t>
-        </is>
-      </c>
-      <c r="E117" s="11" t="n">
-        <v/>
+          <t>Maisons-Alfort</t>
+        </is>
+      </c>
+      <c r="E117" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F117" s="11" t="inlineStr">
         <is>
@@ -9078,14 +9094,14 @@
       </c>
       <c r="I117" s="11" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>05/02/2025</t>
         </is>
       </c>
       <c r="J117" s="11" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="K117" s="11" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="L117" s="11" t="inlineStr"/>
       <c r="M117" s="11" t="inlineStr"/>
@@ -9102,12 +9118,12 @@
     <row r="118">
       <c r="A118" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B118" s="15" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C118" s="15" t="inlineStr">
@@ -9117,7 +9133,7 @@
       </c>
       <c r="D118" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E118" s="15" t="n">
@@ -9135,19 +9151,19 @@
       </c>
       <c r="H118" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I118" s="15" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J118" s="15" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="K118" s="15" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="L118" s="15" t="inlineStr"/>
       <c r="M118" s="15" t="inlineStr"/>
@@ -9164,22 +9180,22 @@
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E119" s="11" t="n">
@@ -9187,44 +9203,44 @@
       </c>
       <c r="F119" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G119" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H119" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I119" s="11" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J119" s="11" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="K119" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L119" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34532</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M119" s="11" t="inlineStr">
         <is>
-          <t>412263</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N119" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O119" s="12" t="n">
+        <v>240</v>
+      </c>
+      <c r="O119" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P119" s="12" t="n">
@@ -9234,12 +9250,12 @@
     <row r="120">
       <c r="A120" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12292</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B120" s="15" t="inlineStr">
         <is>
-          <t>[CD06] Littéralis expert</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C120" s="15" t="inlineStr">
@@ -9249,7 +9265,7 @@
       </c>
       <c r="D120" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E120" s="15" t="n">
@@ -9265,32 +9281,36 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H120" s="15" t="inlineStr"/>
+      <c r="H120" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I120" s="15" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J120" s="15" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="K120" s="15" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L120" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-25456</t>
+          <t>PDMDEP-28023</t>
         </is>
       </c>
       <c r="M120" s="15" t="inlineStr">
         <is>
-          <t>424152</t>
+          <t>454387</t>
         </is>
       </c>
       <c r="N120" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O120" s="16" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O120" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P120" s="16" t="n">
@@ -9300,24 +9320,26 @@
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C121" s="11" t="inlineStr"/>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
+        </is>
+      </c>
+      <c r="C121" s="11" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E121" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>CD Manche</t>
+        </is>
+      </c>
+      <c r="E121" s="11" t="n">
+        <v/>
       </c>
       <c r="F121" s="11" t="inlineStr">
         <is>
@@ -9331,19 +9353,19 @@
       </c>
       <c r="H121" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I121" s="11" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J121" s="11" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="K121" s="11" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L121" s="11" t="inlineStr"/>
       <c r="M121" s="11" t="inlineStr"/>
@@ -9360,21 +9382,27 @@
     <row r="122">
       <c r="A122" s="14" t="inlineStr">
         <is>
-          <t>PSC-1339</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B122" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
-        </is>
-      </c>
-      <c r="C122" s="15" t="inlineStr"/>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+        </is>
+      </c>
+      <c r="C122" s="15" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D122" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
-        </is>
-      </c>
-      <c r="E122" s="15" t="inlineStr"/>
+          <t xml:space="preserve">Asnieres sur Seine </t>
+        </is>
+      </c>
+      <c r="E122" s="15" t="n">
+        <v/>
+      </c>
       <c r="F122" s="15" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -9382,35 +9410,31 @@
       </c>
       <c r="G122" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H122" s="15" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H122" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I122" s="15" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J122" s="15" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="K122" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L122" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-35312</t>
-        </is>
-      </c>
-      <c r="M122" s="15" t="inlineStr">
-        <is>
-          <t>00177354</t>
-        </is>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="L122" s="15" t="inlineStr"/>
+      <c r="M122" s="15" t="inlineStr"/>
       <c r="N122" s="16" t="n">
-        <v>450</v>
-      </c>
-      <c r="O122" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P122" s="16" t="n">
@@ -9420,21 +9444,27 @@
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>PSC-1288</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
-        </is>
-      </c>
-      <c r="C123" s="11" t="inlineStr"/>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="C123" s="11" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
-        </is>
-      </c>
-      <c r="E123" s="11" t="inlineStr"/>
+          <t>LE MANS METROPOLE</t>
+        </is>
+      </c>
+      <c r="E123" s="11" t="n">
+        <v/>
+      </c>
       <c r="F123" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -9442,23 +9472,35 @@
       </c>
       <c r="G123" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H123" s="11" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H123" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I123" s="11" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J123" s="11" t="n">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="K123" s="11" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="L123" s="11" t="inlineStr"/>
-      <c r="M123" s="11" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="L123" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M123" s="11" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
       <c r="N123" s="12" t="n">
         <v>0</v>
       </c>
@@ -9472,21 +9514,27 @@
     <row r="124">
       <c r="A124" s="14" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PDMDEP-12292</t>
         </is>
       </c>
       <c r="B124" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
-        </is>
-      </c>
-      <c r="C124" s="15" t="inlineStr"/>
+          <t>[CD06] Littéralis expert</t>
+        </is>
+      </c>
+      <c r="C124" s="15" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D124" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
-        </is>
-      </c>
-      <c r="E124" s="15" t="inlineStr"/>
+          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
+        </is>
+      </c>
+      <c r="E124" s="15" t="n">
+        <v/>
+      </c>
       <c r="F124" s="15" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -9500,23 +9548,23 @@
       <c r="H124" s="15" t="inlineStr"/>
       <c r="I124" s="15" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J124" s="15" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="K124" s="15" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L124" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33362</t>
+          <t>PDMDEP-25456</t>
         </is>
       </c>
       <c r="M124" s="15" t="inlineStr">
         <is>
-          <t>00167140</t>
+          <t>424152</t>
         </is>
       </c>
       <c r="N124" s="16" t="n">
@@ -9532,89 +9580,321 @@
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>PSC-1047</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C125" s="11" t="inlineStr"/>
       <c r="D125" s="11" t="inlineStr">
         <is>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E125" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
+      <c r="F125" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G125" s="11" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H125" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I125" s="11" t="inlineStr">
+        <is>
+          <t>03/09/2023</t>
+        </is>
+      </c>
+      <c r="J125" s="11" t="n">
+        <v>37</v>
+      </c>
+      <c r="K125" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L125" s="11" t="inlineStr"/>
+      <c r="M125" s="11" t="inlineStr"/>
+      <c r="N125" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="14" t="inlineStr">
+        <is>
+          <t>PSC-1339</t>
+        </is>
+      </c>
+      <c r="B126" s="15" t="inlineStr">
+        <is>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
+        </is>
+      </c>
+      <c r="C126" s="15" t="inlineStr"/>
+      <c r="D126" s="15" t="inlineStr">
+        <is>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
+        </is>
+      </c>
+      <c r="E126" s="15" t="inlineStr"/>
+      <c r="F126" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G126" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H126" s="15" t="inlineStr"/>
+      <c r="I126" s="15" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="J126" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="K126" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-35312</t>
+        </is>
+      </c>
+      <c r="M126" s="15" t="inlineStr">
+        <is>
+          <t>00177354</t>
+        </is>
+      </c>
+      <c r="N126" s="16" t="n">
+        <v>450</v>
+      </c>
+      <c r="O126" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="10" t="inlineStr">
+        <is>
+          <t>PSC-1288</t>
+        </is>
+      </c>
+      <c r="B127" s="11" t="inlineStr">
+        <is>
+          <t>Mairie d'Aubignan</t>
+        </is>
+      </c>
+      <c r="C127" s="11" t="inlineStr"/>
+      <c r="D127" s="11" t="inlineStr">
+        <is>
+          <t>Mairie d'Aubignan</t>
+        </is>
+      </c>
+      <c r="E127" s="11" t="inlineStr"/>
+      <c r="F127" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G127" s="11" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H127" s="11" t="inlineStr"/>
+      <c r="I127" s="11" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="J127" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K127" s="11" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="L127" s="11" t="inlineStr"/>
+      <c r="M127" s="11" t="inlineStr"/>
+      <c r="N127" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P127" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="14" t="inlineStr">
+        <is>
+          <t>PSC-1270</t>
+        </is>
+      </c>
+      <c r="B128" s="15" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="C128" s="15" t="inlineStr"/>
+      <c r="D128" s="15" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="E128" s="15" t="inlineStr"/>
+      <c r="F128" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G128" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H128" s="15" t="inlineStr"/>
+      <c r="I128" s="15" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="J128" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="K128" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L128" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M128" s="15" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
+      <c r="N128" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="10" t="inlineStr">
+        <is>
+          <t>PSC-1047</t>
+        </is>
+      </c>
+      <c r="B129" s="11" t="inlineStr">
+        <is>
           <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
         </is>
       </c>
-      <c r="E125" s="11" t="inlineStr"/>
-      <c r="F125" s="11" t="inlineStr">
+      <c r="C129" s="11" t="inlineStr"/>
+      <c r="D129" s="11" t="inlineStr">
+        <is>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E129" s="11" t="inlineStr"/>
+      <c r="F129" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="G125" s="11" t="inlineStr">
-        <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H125" s="11" t="inlineStr"/>
-      <c r="I125" s="11" t="inlineStr">
+      <c r="G129" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H129" s="11" t="inlineStr"/>
+      <c r="I129" s="11" t="inlineStr">
         <is>
           <t>04/11/2025</t>
         </is>
       </c>
-      <c r="J125" s="11" t="n">
+      <c r="J129" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="K125" s="11" t="n">
+      <c r="K129" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="L125" s="11" t="inlineStr">
+      <c r="L129" s="11" t="inlineStr">
         <is>
           <t>PDMDEP-26768</t>
         </is>
       </c>
-      <c r="M125" s="11" t="inlineStr">
+      <c r="M129" s="11" t="inlineStr">
         <is>
           <t>00141775</t>
         </is>
       </c>
-      <c r="N125" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O125" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P125" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="17" t="inlineStr">
+      <c r="N129" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B126" s="17" t="inlineStr"/>
-      <c r="C126" s="17" t="inlineStr"/>
-      <c r="D126" s="17" t="inlineStr"/>
-      <c r="E126" s="17" t="inlineStr"/>
-      <c r="F126" s="17" t="inlineStr"/>
-      <c r="G126" s="17" t="inlineStr"/>
-      <c r="H126" s="17" t="inlineStr"/>
-      <c r="I126" s="17" t="inlineStr"/>
-      <c r="J126" s="17" t="inlineStr"/>
-      <c r="K126" s="17" t="inlineStr"/>
-      <c r="L126" s="17" t="inlineStr"/>
-      <c r="M126" s="17" t="inlineStr"/>
-      <c r="N126" s="18" t="n">
-        <v>123627.162</v>
-      </c>
-      <c r="O126" s="18" t="n">
+      <c r="B130" s="17" t="inlineStr"/>
+      <c r="C130" s="17" t="inlineStr"/>
+      <c r="D130" s="17" t="inlineStr"/>
+      <c r="E130" s="17" t="inlineStr"/>
+      <c r="F130" s="17" t="inlineStr"/>
+      <c r="G130" s="17" t="inlineStr"/>
+      <c r="H130" s="17" t="inlineStr"/>
+      <c r="I130" s="17" t="inlineStr"/>
+      <c r="J130" s="17" t="inlineStr"/>
+      <c r="K130" s="17" t="inlineStr"/>
+      <c r="L130" s="17" t="inlineStr"/>
+      <c r="M130" s="17" t="inlineStr"/>
+      <c r="N130" s="18" t="n">
+        <v>123351.162</v>
+      </c>
+      <c r="O130" s="18" t="n">
         <v>1518.9</v>
       </c>
-      <c r="P126" s="18" t="n">
-        <v>29.74</v>
+      <c r="P130" s="18" t="n">
+        <v>29.3</v>
       </c>
     </row>
   </sheetData>
@@ -9741,6 +10021,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId119"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A125" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId125"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10498,7 +10782,7 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>27.25</v>
+        <v>28</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>9.75</v>
@@ -10507,17 +10791,17 @@
         <v>1.08</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>38.08</v>
+        <v>38.83</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>5.5</v>
+        <v>6.75</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>508.2</v>
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>7.6%</t>
         </is>
       </c>
     </row>
@@ -10559,7 +10843,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>24.25</v>
+        <v>25.58</v>
       </c>
     </row>
   </sheetData>
@@ -10644,10 +10928,10 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>497643</v>
+        <v>503361</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>198140</v>
+        <v>203858</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>299503</v>
@@ -10669,10 +10953,10 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>256462</v>
+        <v>262180</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>60243</v>
+        <v>65961</v>
       </c>
       <c r="D6" s="25" t="n">
         <v>196219</v>
@@ -10723,7 +11007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -10747,7 +11031,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 4 commande(s)</t>
+          <t>Épics créées ce mois — 5 commande(s)</t>
         </is>
       </c>
     </row>
@@ -10802,12 +11086,12 @@
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-36214</t>
+          <t>PDMDEP-36236</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-36205</t>
+          <t>PDMDEP-36230</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
@@ -10817,7 +11101,7 @@
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>COMME DE FECAMP</t>
+          <t>COMMUNE DE QUIBERON</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -10827,7 +11111,7 @@
       </c>
       <c r="F5" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
@@ -10837,7 +11121,7 @@
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>00176659</t>
+          <t>00183980</t>
         </is>
       </c>
       <c r="I5" s="25" t="n">
@@ -10847,22 +11131,22 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36181</t>
+          <t>PDMDEP-36214</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36174</t>
+          <t>PDMDEP-36205</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE AURAY</t>
+          <t>COMME DE FECAMP</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -10882,7 +11166,7 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>00183814</t>
+          <t>00176659</t>
         </is>
       </c>
       <c r="I6" s="26" t="n">
@@ -10892,12 +11176,12 @@
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-36197</t>
+          <t>PDMDEP-36181</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-36190</t>
+          <t>PDMDEP-36174</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
@@ -10907,17 +11191,17 @@
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BAUGE-EN-ANJOU</t>
+          <t>COMMUNE DE AURAY</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="F7" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G7" s="15" t="inlineStr">
@@ -10927,7 +11211,7 @@
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>00183894</t>
+          <t>00183814</t>
         </is>
       </c>
       <c r="I7" s="25" t="n">
@@ -10937,73 +11221,97 @@
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
+          <t>PDMDEP-36197</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-36190</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>COMMUNE DE BAUGE-EN-ANJOU</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>00183894</t>
+        </is>
+      </c>
+      <c r="I8" s="26" t="n">
+        <v>5718</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
           <t>PDMDEP-36148</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>PDMDEP-36144</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>01/10/2026</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>VILLE DE VILLEFRANCHE SUR SAONE</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E9" s="15" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="F9" s="15" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="G9" s="15" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H8" s="11" t="inlineStr">
+      <c r="H9" s="15" t="inlineStr">
         <is>
           <t>00183228</t>
         </is>
       </c>
-      <c r="I8" s="26" t="n">
-        <v>2310</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="n"/>
-      <c r="C9" s="17" t="n"/>
-      <c r="D9" s="17" t="n"/>
-      <c r="E9" s="17" t="n"/>
-      <c r="F9" s="17" t="n"/>
-      <c r="G9" s="17" t="n"/>
-      <c r="H9" s="17" t="inlineStr">
-        <is>
-          <t>4 commande(s)</t>
-        </is>
-      </c>
-      <c r="I9" s="24" t="n">
+      <c r="I9" s="25" t="n">
         <v>2310</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="17" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B10" s="17" t="n"/>
@@ -11014,17 +11322,17 @@
       <c r="G10" s="17" t="n"/>
       <c r="H10" s="17" t="inlineStr">
         <is>
-          <t>2 commande(s)</t>
+          <t>5 commande(s)</t>
         </is>
       </c>
       <c r="I10" s="24" t="n">
-        <v>2310</v>
+        <v>8028</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B11" s="17" t="n"/>
@@ -11039,6 +11347,27 @@
         </is>
       </c>
       <c r="I11" s="24" t="n">
+        <v>8028</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="17" t="n"/>
+      <c r="E12" s="17" t="n"/>
+      <c r="F12" s="17" t="n"/>
+      <c r="G12" s="17" t="n"/>
+      <c r="H12" s="17" t="inlineStr">
+        <is>
+          <t>3 commande(s)</t>
+        </is>
+      </c>
+      <c r="I12" s="24" t="n">
         <v>0</v>
       </c>
     </row>

--- a/jira_export_2026-10-06.xlsx
+++ b/jira_export_2026-10-06.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>1,519 €</t>
+          <t>2,445 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -767,7 +767,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>792 €</t>
+          <t>1,718 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>86 h</t>
+          <t>99 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>289</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P130"/>
+  <dimension ref="A1:P131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -949,7 +949,7 @@
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
     <col width="26" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
@@ -1173,7 +1173,7 @@
         <v>1</v>
       </c>
       <c r="K6" s="15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L6" s="15" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>[VILLE DE SURESNES] - Ajout du module Coordination</t>
+          <t>[VILLE DE SURESNES] - Ajout module Coordination &amp; Accomp (OnPrem)</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
@@ -1317,7 +1317,7 @@
         <v>1</v>
       </c>
       <c r="K8" s="15" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="L8" s="15" t="inlineStr">
         <is>
@@ -1610,10 +1610,10 @@
         </is>
       </c>
       <c r="N12" s="16" t="n">
-        <v>1852.8</v>
-      </c>
-      <c r="O12" s="13" t="n">
-        <v>0</v>
+        <v>926.4</v>
+      </c>
+      <c r="O12" s="16" t="n">
+        <v>926.4</v>
       </c>
       <c r="P12" s="16" t="n">
         <v>0</v>
@@ -1669,7 +1669,7 @@
         <v>1</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>0.25</v>
+        <v>3.25</v>
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>4</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         <v>4</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>4</v>
       </c>
       <c r="K54" s="15" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="L54" s="15" t="inlineStr">
         <is>
@@ -9444,12 +9444,12 @@
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr">
@@ -9459,7 +9459,7 @@
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E123" s="11" t="n">
@@ -9475,32 +9475,20 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H123" s="11" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H123" s="11" t="inlineStr"/>
       <c r="I123" s="11" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J123" s="11" t="n">
         <v>37</v>
       </c>
       <c r="K123" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="L123" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M123" s="11" t="inlineStr">
-        <is>
-          <t>412263</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L123" s="11" t="inlineStr"/>
+      <c r="M123" s="11" t="inlineStr"/>
       <c r="N123" s="12" t="n">
         <v>0</v>
       </c>
@@ -9514,22 +9502,22 @@
     <row r="124">
       <c r="A124" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12292</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B124" s="15" t="inlineStr">
         <is>
-          <t>[CD06] Littéralis expert</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C124" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D124" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
+          <t>LE MANS METROPOLE</t>
         </is>
       </c>
       <c r="E124" s="15" t="n">
@@ -9542,29 +9530,33 @@
       </c>
       <c r="G124" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H124" s="15" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H124" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I124" s="15" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J124" s="15" t="n">
         <v>37</v>
       </c>
       <c r="K124" s="15" t="n">
-        <v>0.75</v>
+        <v>5</v>
       </c>
       <c r="L124" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-25456</t>
+          <t>PDMDEP-34532</t>
         </is>
       </c>
       <c r="M124" s="15" t="inlineStr">
         <is>
-          <t>424152</t>
+          <t>412263</t>
         </is>
       </c>
       <c r="N124" s="16" t="n">
@@ -9580,24 +9572,26 @@
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12292</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C125" s="11" t="inlineStr"/>
+          <t>[CD06] Littéralis expert</t>
+        </is>
+      </c>
+      <c r="C125" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E125" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
+        </is>
+      </c>
+      <c r="E125" s="11" t="n">
+        <v/>
       </c>
       <c r="F125" s="11" t="inlineStr">
         <is>
@@ -9606,27 +9600,31 @@
       </c>
       <c r="G125" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H125" s="11" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H125" s="11" t="inlineStr"/>
       <c r="I125" s="11" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J125" s="11" t="n">
         <v>37</v>
       </c>
       <c r="K125" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L125" s="11" t="inlineStr"/>
-      <c r="M125" s="11" t="inlineStr"/>
+        <v>0.75</v>
+      </c>
+      <c r="L125" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-25456</t>
+        </is>
+      </c>
+      <c r="M125" s="11" t="inlineStr">
+        <is>
+          <t>424152</t>
+        </is>
+      </c>
       <c r="N125" s="12" t="n">
         <v>0</v>
       </c>
@@ -9640,21 +9638,25 @@
     <row r="126">
       <c r="A126" s="14" t="inlineStr">
         <is>
-          <t>PSC-1339</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B126" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C126" s="15" t="inlineStr"/>
       <c r="D126" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
-        </is>
-      </c>
-      <c r="E126" s="15" t="inlineStr"/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E126" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
       <c r="F126" s="15" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -9662,35 +9664,31 @@
       </c>
       <c r="G126" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H126" s="15" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H126" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I126" s="15" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J126" s="15" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="K126" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L126" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-35312</t>
-        </is>
-      </c>
-      <c r="M126" s="15" t="inlineStr">
-        <is>
-          <t>00177354</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L126" s="15" t="inlineStr"/>
+      <c r="M126" s="15" t="inlineStr"/>
       <c r="N126" s="16" t="n">
-        <v>450</v>
-      </c>
-      <c r="O126" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P126" s="16" t="n">
@@ -9700,18 +9698,18 @@
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>PSC-1288</t>
+          <t>PSC-1339</t>
         </is>
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="C127" s="11" t="inlineStr"/>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="E127" s="11" t="inlineStr"/>
@@ -9722,27 +9720,35 @@
       </c>
       <c r="G127" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H127" s="11" t="inlineStr"/>
       <c r="I127" s="11" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J127" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K127" s="11" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="L127" s="11" t="inlineStr"/>
-      <c r="M127" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L127" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-35312</t>
+        </is>
+      </c>
+      <c r="M127" s="11" t="inlineStr">
+        <is>
+          <t>00177354</t>
+        </is>
+      </c>
       <c r="N127" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O127" s="12" t="n">
+        <v>450</v>
+      </c>
+      <c r="O127" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P127" s="12" t="n">
@@ -9752,18 +9758,18 @@
     <row r="128">
       <c r="A128" s="14" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1288</t>
         </is>
       </c>
       <c r="B128" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="C128" s="15" t="inlineStr"/>
       <c r="D128" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="E128" s="15" t="inlineStr"/>
@@ -9774,31 +9780,23 @@
       </c>
       <c r="G128" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H128" s="15" t="inlineStr"/>
       <c r="I128" s="15" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J128" s="15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K128" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L128" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M128" s="15" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+        <v>0.08</v>
+      </c>
+      <c r="L128" s="15" t="inlineStr"/>
+      <c r="M128" s="15" t="inlineStr"/>
       <c r="N128" s="16" t="n">
         <v>0</v>
       </c>
@@ -9812,18 +9810,18 @@
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>PSC-1047</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C129" s="11" t="inlineStr"/>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E129" s="11" t="inlineStr"/>
@@ -9840,61 +9838,121 @@
       <c r="H129" s="11" t="inlineStr"/>
       <c r="I129" s="11" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="J129" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="K129" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L129" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M129" s="11" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
+      <c r="N129" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="14" t="inlineStr">
+        <is>
+          <t>PSC-1047</t>
+        </is>
+      </c>
+      <c r="B130" s="15" t="inlineStr">
+        <is>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+        </is>
+      </c>
+      <c r="C130" s="15" t="inlineStr"/>
+      <c r="D130" s="15" t="inlineStr">
+        <is>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E130" s="15" t="inlineStr"/>
+      <c r="F130" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G130" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H130" s="15" t="inlineStr"/>
+      <c r="I130" s="15" t="inlineStr">
+        <is>
           <t>04/11/2025</t>
         </is>
       </c>
-      <c r="J129" s="11" t="n">
+      <c r="J130" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="K129" s="11" t="n">
+      <c r="K130" s="15" t="n">
         <v>0.25</v>
       </c>
-      <c r="L129" s="11" t="inlineStr">
+      <c r="L130" s="15" t="inlineStr">
         <is>
           <t>PDMDEP-26768</t>
         </is>
       </c>
-      <c r="M129" s="11" t="inlineStr">
+      <c r="M130" s="15" t="inlineStr">
         <is>
           <t>00141775</t>
         </is>
       </c>
-      <c r="N129" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O129" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P129" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="17" t="inlineStr">
+      <c r="N130" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O130" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P130" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B130" s="17" t="inlineStr"/>
-      <c r="C130" s="17" t="inlineStr"/>
-      <c r="D130" s="17" t="inlineStr"/>
-      <c r="E130" s="17" t="inlineStr"/>
-      <c r="F130" s="17" t="inlineStr"/>
-      <c r="G130" s="17" t="inlineStr"/>
-      <c r="H130" s="17" t="inlineStr"/>
-      <c r="I130" s="17" t="inlineStr"/>
-      <c r="J130" s="17" t="inlineStr"/>
-      <c r="K130" s="17" t="inlineStr"/>
-      <c r="L130" s="17" t="inlineStr"/>
-      <c r="M130" s="17" t="inlineStr"/>
-      <c r="N130" s="18" t="n">
-        <v>123351.162</v>
-      </c>
-      <c r="O130" s="18" t="n">
-        <v>1518.9</v>
-      </c>
-      <c r="P130" s="18" t="n">
-        <v>29.3</v>
+      <c r="B131" s="17" t="inlineStr"/>
+      <c r="C131" s="17" t="inlineStr"/>
+      <c r="D131" s="17" t="inlineStr"/>
+      <c r="E131" s="17" t="inlineStr"/>
+      <c r="F131" s="17" t="inlineStr"/>
+      <c r="G131" s="17" t="inlineStr"/>
+      <c r="H131" s="17" t="inlineStr"/>
+      <c r="I131" s="17" t="inlineStr"/>
+      <c r="J131" s="17" t="inlineStr"/>
+      <c r="K131" s="17" t="inlineStr"/>
+      <c r="L131" s="17" t="inlineStr"/>
+      <c r="M131" s="17" t="inlineStr"/>
+      <c r="N131" s="18" t="n">
+        <v>122424.762</v>
+      </c>
+      <c r="O131" s="18" t="n">
+        <v>2445.3</v>
+      </c>
+      <c r="P131" s="18" t="n">
+        <v>39.7</v>
       </c>
     </row>
   </sheetData>
@@ -10025,6 +10083,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId123"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId124"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A130" r:id="rId126"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10782,16 +10841,16 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>28</v>
+        <v>37.5</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>9.75</v>
+        <v>10</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>1.08</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>38.83</v>
+        <v>48.58</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>6.75</v>
@@ -10801,7 +10860,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>9.6%</t>
         </is>
       </c>
     </row>
@@ -10843,7 +10902,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>25.58</v>
+        <v>29.08</v>
       </c>
     </row>
   </sheetData>
@@ -10928,10 +10987,10 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>503361</v>
+        <v>502435</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>203858</v>
+        <v>202932</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>299503</v>
@@ -10978,10 +11037,10 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>241181</v>
+        <v>240255</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>137897</v>
+        <v>136970</v>
       </c>
       <c r="D7" s="26" t="n">
         <v>103284</v>
@@ -11007,17 +11066,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -11031,7 +11090,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 5 commande(s)</t>
+          <t>Épics créées ce mois — 13 commande(s)</t>
         </is>
       </c>
     </row>
@@ -11221,22 +11280,22 @@
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36197</t>
+          <t>PDMDEP-36259</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36190</t>
+          <t>PDMDEP-36247</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BAUGE-EN-ANJOU</t>
+          <t>COMMUNE D AVIGNON</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -11254,120 +11313,476 @@
           <t>Services</t>
         </is>
       </c>
-      <c r="H8" s="11" t="inlineStr">
-        <is>
-          <t>00183894</t>
-        </is>
-      </c>
+      <c r="H8" s="11" t="inlineStr"/>
       <c r="I8" s="26" t="n">
-        <v>5718</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
+          <t>PDMDEP-36258</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-36247</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>COMMUNE D AVIGNON</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="G9" s="15" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H9" s="15" t="inlineStr">
+        <is>
+          <t>https:</t>
+        </is>
+      </c>
+      <c r="I9" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-36257</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-36247</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>COMMUNE D AVIGNON</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>infos</t>
+        </is>
+      </c>
+      <c r="I10" s="26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-36256</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-36247</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>COMMUNE D AVIGNON</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="G11" s="15" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="I11" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-36255</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-36247</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>COMMUNE D AVIGNON</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>sogetask</t>
+        </is>
+      </c>
+      <c r="I12" s="26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-36254</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-36247</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>COMMUNE D AVIGNON</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="G13" s="15" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H13" s="15" t="inlineStr">
+        <is>
+          <t>1849345</t>
+        </is>
+      </c>
+      <c r="I13" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-36253</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-36247</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>COMMUNE D AVIGNON</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>apps.sogelink.fr</t>
+        </is>
+      </c>
+      <c r="I14" s="26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-36252</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-36247</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>COMMUNE D AVIGNON</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="G15" s="15" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H15" s="15" t="inlineStr">
+        <is>
+          <t>tasks</t>
+        </is>
+      </c>
+      <c r="I15" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-36197</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-36190</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>COMMUNE DE BAUGE-EN-ANJOU</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H16" s="11" t="inlineStr">
+        <is>
+          <t>00183894</t>
+        </is>
+      </c>
+      <c r="I16" s="26" t="n">
+        <v>5718</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
           <t>PDMDEP-36148</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>PDMDEP-36144</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <t>01/10/2026</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D17" s="15" t="inlineStr">
         <is>
           <t>VILLE DE VILLEFRANCHE SUR SAONE</t>
         </is>
       </c>
-      <c r="E9" s="15" t="inlineStr">
+      <c r="E17" s="15" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F9" s="15" t="inlineStr">
+      <c r="F17" s="15" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G9" s="15" t="inlineStr">
+      <c r="G17" s="15" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H9" s="15" t="inlineStr">
+      <c r="H17" s="15" t="inlineStr">
         <is>
           <t>00183228</t>
         </is>
       </c>
-      <c r="I9" s="25" t="n">
+      <c r="I17" s="25" t="n">
         <v>2310</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B10" s="17" t="n"/>
-      <c r="C10" s="17" t="n"/>
-      <c r="D10" s="17" t="n"/>
-      <c r="E10" s="17" t="n"/>
-      <c r="F10" s="17" t="n"/>
-      <c r="G10" s="17" t="n"/>
-      <c r="H10" s="17" t="inlineStr">
-        <is>
-          <t>5 commande(s)</t>
-        </is>
-      </c>
-      <c r="I10" s="24" t="n">
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="17" t="n"/>
+      <c r="D18" s="17" t="n"/>
+      <c r="E18" s="17" t="n"/>
+      <c r="F18" s="17" t="n"/>
+      <c r="G18" s="17" t="n"/>
+      <c r="H18" s="17" t="inlineStr">
+        <is>
+          <t>13 commande(s)</t>
+        </is>
+      </c>
+      <c r="I18" s="24" t="n">
         <v>8028</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>dont Littéralis</t>
         </is>
       </c>
-      <c r="B11" s="17" t="n"/>
-      <c r="C11" s="17" t="n"/>
-      <c r="D11" s="17" t="n"/>
-      <c r="E11" s="17" t="n"/>
-      <c r="F11" s="17" t="n"/>
-      <c r="G11" s="17" t="n"/>
-      <c r="H11" s="17" t="inlineStr">
-        <is>
-          <t>2 commande(s)</t>
-        </is>
-      </c>
-      <c r="I11" s="24" t="n">
+      <c r="B19" s="17" t="n"/>
+      <c r="C19" s="17" t="n"/>
+      <c r="D19" s="17" t="n"/>
+      <c r="E19" s="17" t="n"/>
+      <c r="F19" s="17" t="n"/>
+      <c r="G19" s="17" t="n"/>
+      <c r="H19" s="17" t="inlineStr">
+        <is>
+          <t>10 commande(s)</t>
+        </is>
+      </c>
+      <c r="I19" s="24" t="n">
         <v>8028</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>dont GEODP</t>
         </is>
       </c>
-      <c r="B12" s="17" t="n"/>
-      <c r="C12" s="17" t="n"/>
-      <c r="D12" s="17" t="n"/>
-      <c r="E12" s="17" t="n"/>
-      <c r="F12" s="17" t="n"/>
-      <c r="G12" s="17" t="n"/>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="17" t="n"/>
+      <c r="G20" s="17" t="n"/>
+      <c r="H20" s="17" t="inlineStr">
         <is>
           <t>3 commande(s)</t>
         </is>
       </c>
-      <c r="I12" s="24" t="n">
+      <c r="I20" s="24" t="n">
         <v>0</v>
       </c>
     </row>
